--- a/data/proteomics/organell_protein_ratio_tao2.xlsx
+++ b/data/proteomics/organell_protein_ratio_tao2.xlsx
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3768291948768153</v>
+        <v>0.3768291948768152</v>
       </c>
       <c r="C2" t="n">
         <v>0.001132151698543643</v>
@@ -1159,13 +1159,13 @@
         <v>0.02796931597783909</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1442851810207112</v>
+        <v>0.144285181020711</v>
       </c>
       <c r="G2" t="n">
         <v>0.5368318577506769</v>
       </c>
       <c r="H2" t="n">
-        <v>0.153390242886723</v>
+        <v>0.1533902428867231</v>
       </c>
       <c r="I2" t="n">
         <v>0.00982076731278198</v>
@@ -1177,28 +1177,28 @@
         <v>0.007411843722660433</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03923806603228647</v>
+        <v>0.03923806603228645</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003874746700063029</v>
+        <v>0.00387474670006303</v>
       </c>
       <c r="N2" t="n">
         <v>0.01658881084334536</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003241068740903496</v>
+        <v>0.003241068740903495</v>
       </c>
       <c r="P2" t="n">
         <v>0.008583817677694554</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003038339006291353</v>
+        <v>0.002597669596774738</v>
       </c>
       <c r="R2" t="n">
         <v>0.005928326867799747</v>
       </c>
       <c r="S2" t="n">
-        <v>0.005448069764076993</v>
+        <v>0.005448069764076999</v>
       </c>
       <c r="T2" t="n">
         <v>0.01676481417784167</v>
@@ -1219,16 +1219,16 @@
         <v>0.00277904438078973</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004488893708375061</v>
+        <v>0.004488893708375062</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0203529154463612</v>
+        <v>0.02035291544636118</v>
       </c>
       <c r="AB2" t="n">
         <v>0.00110025581645589</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.02861449377689426</v>
+        <v>0.02861449377689424</v>
       </c>
       <c r="AD2" t="n">
         <v>6.293266183093604e-05</v>
@@ -1237,7 +1237,7 @@
         <v>2.879704407604192e-05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.04640565340505701</v>
+        <v>0.04640565340505702</v>
       </c>
       <c r="AG2" t="n">
         <v>0.0182294097391866</v>
@@ -1246,10 +1246,10 @@
         <v>0.002497131950886001</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0007245952945119369</v>
+        <v>0.0007245952945119374</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.002523246809566364</v>
+        <v>0.002523246809566363</v>
       </c>
       <c r="AK2" t="n">
         <v>0.01770357406143309</v>
@@ -1264,7 +1264,7 @@
         <v>0.0001879706679759903</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.001038116023557725</v>
+        <v>0.001038116023557726</v>
       </c>
       <c r="AP2" t="n">
         <v>0.0007866918669784848</v>
@@ -1294,13 +1294,13 @@
         <v>0.001782223229634296</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.05110038990234938</v>
+        <v>0.05110038990234936</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0005147931182266694</v>
+        <v>0.0005147931182266695</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.0002646001060258181</v>
+        <v>0.0002646001060258182</v>
       </c>
       <c r="BB2" t="n">
         <v>0.02645251988049442</v>
@@ -1315,7 +1315,7 @@
         <v>0.001190273228478583</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.001260923307931316</v>
+        <v>0.001260923307931317</v>
       </c>
       <c r="BG2" t="n">
         <v>0.001815631860843193</v>
@@ -1324,13 +1324,13 @@
         <v>0.006535275947971199</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0003410153390013256</v>
+        <v>0.0003410153390013257</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.00100276485049489</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.007465223045612305</v>
+        <v>0.0074652230456123</v>
       </c>
       <c r="BL2" t="n">
         <v>0.0001385114071495396</v>
@@ -1345,7 +1345,7 @@
         <v>7.30955997707067e-05</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0003739942490058977</v>
+        <v>0.0003739942490058976</v>
       </c>
       <c r="BQ2" t="n">
         <v>0.0004997864183314714</v>
@@ -1372,7 +1372,7 @@
         <v>0.001572969846242717</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0004691766294853187</v>
+        <v>0.0004691766294853186</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.0004915161852386597</v>
@@ -1429,7 +1429,7 @@
         <v>0.002304618940482489</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.0004943506417664811</v>
+        <v>0.0004943506417664812</v>
       </c>
       <c r="CS2" t="n">
         <v>0.0001997123109852517</v>
@@ -1447,7 +1447,7 @@
         <v>0.0004185428272079075</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.002789811608029413</v>
+        <v>0.002789811608029414</v>
       </c>
       <c r="CY2" t="n">
         <v>0.0002265152177768358</v>
@@ -1456,10 +1456,10 @@
         <v>0.0004745975157630369</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0004433886338713067</v>
+        <v>0.0004433886338713066</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0004975938997294175</v>
+        <v>0.0004975938997294174</v>
       </c>
       <c r="DC2" t="n">
         <v>5.067118891863229e-05</v>
@@ -1492,13 +1492,13 @@
         <v>0.0002747265544247348</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.0002176634659638817</v>
+        <v>0.0002176634659638818</v>
       </c>
       <c r="DN2" t="n">
         <v>4.970591443250374e-05</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.002444612815262921</v>
+        <v>0.00244461281526292</v>
       </c>
       <c r="DP2" t="n">
         <v>0.1055178157988777</v>
@@ -1531,19 +1531,19 @@
         <v>0.0002151997034669004</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.0004861730729641607</v>
+        <v>0.0004861730729641608</v>
       </c>
       <c r="EA2" t="n">
         <v>0.0006716585259983622</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.0004413261305732981</v>
+        <v>0.0004413261305732982</v>
       </c>
       <c r="EC2" t="n">
         <v>0.01381315986830695</v>
       </c>
       <c r="ED2" t="n">
-        <v>4.13783764393886e-05</v>
+        <v>4.137837643938859e-05</v>
       </c>
       <c r="EE2" t="n">
         <v>0.0003167892112404957</v>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3804552307818092</v>
+        <v>0.3804552307818095</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001320160335063421</v>
+        <v>0.00132016033506342</v>
       </c>
       <c r="D3" t="n">
         <v>0.001627248963576847</v>
@@ -1594,16 +1594,16 @@
         <v>0.03088059334224113</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1509101256705734</v>
+        <v>0.1509101256705731</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5222899840034262</v>
+        <v>0.5222899840034256</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1693695005601439</v>
+        <v>0.1693695005601436</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01272541058396212</v>
+        <v>0.01272541058396213</v>
       </c>
       <c r="J3" t="n">
         <v>0.01966881702894218</v>
@@ -1612,7 +1612,7 @@
         <v>0.009101773769533836</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04135308259720926</v>
+        <v>0.04135308259720927</v>
       </c>
       <c r="M3" t="n">
         <v>0.003876573168787522</v>
@@ -1621,13 +1621,13 @@
         <v>0.01781832751953827</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003532351729570324</v>
+        <v>0.003532351729570323</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009424272656281599</v>
+        <v>0.009424272656281605</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003416434055986873</v>
+        <v>0.002967647280086907</v>
       </c>
       <c r="R3" t="n">
         <v>0.006671524409867072</v>
@@ -1651,7 +1651,7 @@
         <v>0.0002096692014278634</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003060109610215866</v>
+        <v>0.003060109610215864</v>
       </c>
       <c r="Z3" t="n">
         <v>0.004886034659579245</v>
@@ -1663,28 +1663,28 @@
         <v>0.001205469589752735</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.03054085609221925</v>
+        <v>0.03054085609221922</v>
       </c>
       <c r="AD3" t="n">
         <v>6.696160691778797e-05</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.934383533903402e-05</v>
+        <v>2.934383533903403e-05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.04963455621733456</v>
+        <v>0.04963455621733457</v>
       </c>
       <c r="AG3" t="n">
         <v>0.01798793815324417</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.002650696680620222</v>
+        <v>0.002650696680620223</v>
       </c>
       <c r="AI3" t="n">
         <v>0.0007313609238601283</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.00279335608118473</v>
+        <v>0.002793356081184731</v>
       </c>
       <c r="AK3" t="n">
         <v>0.01940813104827208</v>
@@ -1723,13 +1723,13 @@
         <v>0.002315195332391406</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.01442326915143952</v>
+        <v>0.01442326915143953</v>
       </c>
       <c r="AX3" t="n">
         <v>0.001758127160510318</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.05076988925978831</v>
+        <v>0.0507698892597883</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.0005375543179628195</v>
@@ -1738,10 +1738,10 @@
         <v>0.0002903848586063492</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.02658187400978725</v>
+        <v>0.02658187400978724</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.009993535547268477</v>
+        <v>0.00999353554726848</v>
       </c>
       <c r="BD3" t="n">
         <v>0.01822466964201763</v>
@@ -1759,13 +1759,13 @@
         <v>0.006241537166703641</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0003853972477061496</v>
+        <v>0.0003853972477061495</v>
       </c>
       <c r="BJ3" t="n">
         <v>0.0009260455711801003</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.00777579879654777</v>
+        <v>0.007775798796547776</v>
       </c>
       <c r="BL3" t="n">
         <v>0.0001406156704372236</v>
@@ -1783,13 +1783,13 @@
         <v>0.00040932721348734</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0004901315833782367</v>
+        <v>0.0004901315833782368</v>
       </c>
       <c r="BR3" t="n">
         <v>0.0007530266348114079</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.007630150447227045</v>
+        <v>0.00763015044722705</v>
       </c>
       <c r="BT3" t="n">
         <v>0.004263034989640274</v>
@@ -1801,7 +1801,7 @@
         <v>0.003520903378598084</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.407117380451332e-05</v>
+        <v>3.407117380451333e-05</v>
       </c>
       <c r="BX3" t="n">
         <v>0.001690431604393317</v>
@@ -1813,7 +1813,7 @@
         <v>0.0007644590009047</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0002561006000009094</v>
+        <v>0.0002561006000009095</v>
       </c>
       <c r="CB3" t="n">
         <v>0.0003200079468116968</v>
@@ -1873,7 +1873,7 @@
         <v>0.0006253173727382641</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.000493917787904848</v>
+        <v>0.0004939177879048479</v>
       </c>
       <c r="CV3" t="n">
         <v>0.0005456713944872538</v>
@@ -1888,10 +1888,10 @@
         <v>0.0002390565046032459</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0004802966045816087</v>
+        <v>0.0004802966045816088</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0005542242477225189</v>
+        <v>0.0005542242477225194</v>
       </c>
       <c r="DB3" t="n">
         <v>0.0005400333137177117</v>
@@ -1936,7 +1936,7 @@
         <v>0.00264243668205822</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.09930926869169562</v>
+        <v>0.09930926869169567</v>
       </c>
       <c r="DQ3" t="n">
         <v>4.699815490971136e-05</v>
@@ -1963,13 +1963,13 @@
         <v>0.001096141118452706</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0002173562248200255</v>
+        <v>0.0002173562248200256</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0005407231574283848</v>
+        <v>0.0005407231574283842</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0006086407349358792</v>
+        <v>0.0006086407349358788</v>
       </c>
       <c r="EB3" t="n">
         <v>0.0004870411957452499</v>
@@ -1981,10 +1981,10 @@
         <v>3.541492397520705e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.0003263142171318563</v>
+        <v>0.0003263142171318564</v>
       </c>
       <c r="EF3" t="n">
-        <v>2.54982134917121e-05</v>
+        <v>2.549821349171209e-05</v>
       </c>
       <c r="EG3" t="n">
         <v>0.0001841642091391429</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.347865328215538</v>
+        <v>0.3478653282155376</v>
       </c>
       <c r="C4" t="n">
         <v>0.0008980883803972595</v>
@@ -2029,13 +2029,13 @@
         <v>0.03877560203496943</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1698939931202435</v>
+        <v>0.1698939931202434</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5249719239761547</v>
+        <v>0.5249719239761556</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1828454858289218</v>
+        <v>0.1828454858289217</v>
       </c>
       <c r="I4" t="n">
         <v>0.01345188497120252</v>
@@ -2047,10 +2047,10 @@
         <v>0.007864729814611686</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04206805331419963</v>
+        <v>0.04206805331419958</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009986372781839111</v>
+        <v>0.009986372781839108</v>
       </c>
       <c r="N4" t="n">
         <v>0.02048900088668536</v>
@@ -2059,19 +2059,19 @@
         <v>0.003003126477312455</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01014578246298564</v>
+        <v>0.01014578246298563</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009506081062364289</v>
+        <v>0.002421776729006168</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005376242919750387</v>
+        <v>0.005376242919750383</v>
       </c>
       <c r="S4" t="n">
         <v>0.005759177726387769</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01614518379096859</v>
+        <v>0.01614518379096858</v>
       </c>
       <c r="U4" t="n">
         <v>9.894070994095339e-05</v>
@@ -2083,22 +2083,22 @@
         <v>0.01485365952847897</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001345536163977732</v>
+        <v>0.0001345536163977731</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00367113637078901</v>
+        <v>0.003671136370789009</v>
       </c>
       <c r="Z4" t="n">
         <v>0.003649792913838155</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02283797926899087</v>
+        <v>0.0228379792689909</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0009787961993763551</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.04456515275888989</v>
+        <v>0.0445651527588899</v>
       </c>
       <c r="AD4" t="n">
         <v>5.85643728940809e-05</v>
@@ -2116,7 +2116,7 @@
         <v>0.002313125055196424</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001192984338047973</v>
+        <v>0.001192984338047972</v>
       </c>
       <c r="AJ4" t="n">
         <v>0.002272880332548733</v>
@@ -2143,7 +2143,7 @@
         <v>0.004036960396779889</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005747501814919276</v>
+        <v>0.005747501814919279</v>
       </c>
       <c r="AS4" t="n">
         <v>5.473977402400768e-05</v>
@@ -2161,25 +2161,25 @@
         <v>0.033079410819841</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001246637522146829</v>
+        <v>0.001246637522146828</v>
       </c>
       <c r="AY4" t="n">
         <v>0.04596507698038794</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0007638482331707648</v>
+        <v>0.0007638482331707649</v>
       </c>
       <c r="BA4" t="n">
         <v>0.0002499117291670613</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.03527502634714921</v>
+        <v>0.03527502634714922</v>
       </c>
       <c r="BC4" t="n">
         <v>0.01281455888261207</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01317394942497101</v>
+        <v>0.013173949424971</v>
       </c>
       <c r="BE4" t="n">
         <v>0.001395786145399228</v>
@@ -2200,13 +2200,13 @@
         <v>0.0007753813946489298</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.008639747397040425</v>
+        <v>0.008639747397040421</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0002175626672361455</v>
+        <v>0.0002175626672361456</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.03190890305665484</v>
+        <v>0.03190890305665485</v>
       </c>
       <c r="BN4" t="n">
         <v>0.00182808208280015</v>
@@ -2218,7 +2218,7 @@
         <v>0.0005229580757850047</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0008105205610947148</v>
+        <v>0.0008105205610947146</v>
       </c>
       <c r="BR4" t="n">
         <v>0.000729966529153786</v>
@@ -2230,7 +2230,7 @@
         <v>0.004673272531431944</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.005168632514184037</v>
+        <v>0.005168632514184036</v>
       </c>
       <c r="BV4" t="n">
         <v>0.004577656477999605</v>
@@ -2254,7 +2254,7 @@
         <v>0.0003656584655909981</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0002012926327662043</v>
+        <v>0.0002012926327662042</v>
       </c>
       <c r="CD4" t="n">
         <v>0.0002728882748461901</v>
@@ -2287,7 +2287,7 @@
         <v>3.96570495996935e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0003022717172033369</v>
+        <v>0.0003022717172033368</v>
       </c>
       <c r="CO4" t="n">
         <v>0.001035555564431982</v>
@@ -2299,13 +2299,13 @@
         <v>0.001075228613224232</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.000553976210564736</v>
+        <v>0.0005539762105647359</v>
       </c>
       <c r="CS4" t="n">
         <v>0.0001340264764468637</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0005402680105419461</v>
+        <v>0.000540268010541946</v>
       </c>
       <c r="CU4" t="n">
         <v>0.0003620905417895445</v>
@@ -2314,7 +2314,7 @@
         <v>0.0007135157556556669</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0002845298132970947</v>
+        <v>0.0002845298132970948</v>
       </c>
       <c r="CX4" t="n">
         <v>0.00396071599686278</v>
@@ -2323,19 +2323,19 @@
         <v>0.0001756118887120684</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0003862142793123624</v>
+        <v>0.0003862142793123623</v>
       </c>
       <c r="DA4" t="n">
         <v>0.0007839216417769467</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0006581901975149044</v>
+        <v>0.0006581901975149045</v>
       </c>
       <c r="DC4" t="n">
         <v>8.547531646824605e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.003273209297144348</v>
+        <v>0.00327320929714435</v>
       </c>
       <c r="DE4" t="n">
         <v>0.0001220740373146931</v>
@@ -2350,7 +2350,7 @@
         <v>0.001343972693806654</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0001524322151069398</v>
+        <v>0.0001524322151069399</v>
       </c>
       <c r="DJ4" t="n">
         <v>0.0002470144626051505</v>
@@ -2362,7 +2362,7 @@
         <v>0.0003111060924276907</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0005105808440493645</v>
+        <v>0.0005105808440493644</v>
       </c>
       <c r="DN4" t="n">
         <v>5.483058513720899e-05</v>
@@ -2383,16 +2383,16 @@
         <v>0.001830340785544252</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0009706099471540907</v>
+        <v>0.0009706099471540908</v>
       </c>
       <c r="DU4" t="n">
         <v>0.002140702279316488</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0005368475107017044</v>
+        <v>0.0005368475107017046</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0008884642663115443</v>
+        <v>0.0008884642663115442</v>
       </c>
       <c r="DX4" t="n">
         <v>0.000840275081841446</v>
@@ -2404,7 +2404,7 @@
         <v>0.0003504888700205975</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0006578585030704756</v>
+        <v>0.0006578585030704757</v>
       </c>
       <c r="EB4" t="n">
         <v>0.000422047596441051</v>
@@ -2425,7 +2425,7 @@
         <v>0.0002386510802927683</v>
       </c>
       <c r="EH4" t="n">
-        <v>8.996123483941837e-05</v>
+        <v>8.996123483941838e-05</v>
       </c>
       <c r="EI4" t="n">
         <v>6.563718081817266e-05</v>
@@ -2455,7 +2455,7 @@
         <v>0.3563961401294923</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001500906486734056</v>
+        <v>0.001500906486734055</v>
       </c>
       <c r="D5" t="n">
         <v>0.001886362454107047</v>
@@ -2464,16 +2464,16 @@
         <v>0.04064172839432663</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1832848072933105</v>
+        <v>0.1832848072933106</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4974677757564182</v>
+        <v>0.4974677757564174</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1922909266699244</v>
+        <v>0.1922909266699243</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01604696364747973</v>
+        <v>0.01604696364747974</v>
       </c>
       <c r="J5" t="n">
         <v>0.03500951930393774</v>
@@ -2482,13 +2482,13 @@
         <v>0.01238761467382233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05438336181778326</v>
+        <v>0.05438336181778324</v>
       </c>
       <c r="M5" t="n">
         <v>0.01362312684900071</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02008955505178893</v>
+        <v>0.02008955505178892</v>
       </c>
       <c r="O5" t="n">
         <v>0.002321427234168139</v>
@@ -2497,13 +2497,13 @@
         <v>0.01295269466518753</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01338041352831077</v>
+        <v>0.003224765454510761</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007582446349790085</v>
+        <v>0.007582446349790083</v>
       </c>
       <c r="S5" t="n">
-        <v>0.007367110062484527</v>
+        <v>0.007367110062484525</v>
       </c>
       <c r="T5" t="n">
         <v>0.02359994602000102</v>
@@ -2518,10 +2518,10 @@
         <v>0.01498242419514372</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002332557460290044</v>
+        <v>0.0002332557460290045</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003476660197740435</v>
+        <v>0.003476660197740436</v>
       </c>
       <c r="Z5" t="n">
         <v>0.0051441315682254</v>
@@ -2542,13 +2542,13 @@
         <v>3.420052838903571e-05</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.05038234324876487</v>
+        <v>0.05038234324876485</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.02958781294552845</v>
+        <v>0.02958781294552846</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.003050272939585803</v>
+        <v>0.003050272939585802</v>
       </c>
       <c r="AI5" t="n">
         <v>0.001132765628089293</v>
@@ -2578,43 +2578,43 @@
         <v>0.003745369472464469</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.006613049785733162</v>
+        <v>0.006613049785733164</v>
       </c>
       <c r="AS5" t="n">
         <v>6.339709492786703e-05</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0003614314130918456</v>
+        <v>0.0003614314130918455</v>
       </c>
       <c r="AU5" t="n">
         <v>0.0003991968408366196</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.002718341965158462</v>
+        <v>0.002718341965158463</v>
       </c>
       <c r="AW5" t="n">
         <v>0.01955748551705965</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.00131461691576008</v>
+        <v>0.001314616915760081</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.03761740724333321</v>
+        <v>0.03761740724333319</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0008191105150907961</v>
+        <v>0.0008191105150907963</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0003107353153499922</v>
+        <v>0.0003107353153499921</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.04407038471159334</v>
+        <v>0.04407038471159335</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.01506560063388714</v>
+        <v>0.01506560063388713</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01262006387445931</v>
+        <v>0.01262006387445932</v>
       </c>
       <c r="BE5" t="n">
         <v>0.001745828216746097</v>
@@ -2623,7 +2623,7 @@
         <v>0.001718985082566435</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.00186725356248728</v>
+        <v>0.001867253562487279</v>
       </c>
       <c r="BH5" t="n">
         <v>0.01072635275071449</v>
@@ -2650,7 +2650,7 @@
         <v>0.0001169248531402528</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0005873239981161156</v>
+        <v>0.0005873239981161159</v>
       </c>
       <c r="BQ5" t="n">
         <v>0.0008058698666449622</v>
@@ -2665,13 +2665,13 @@
         <v>0.005406644575785067</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.005664354278832954</v>
+        <v>0.005664354278832955</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.004839135275689603</v>
+        <v>0.004839135275689604</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.697062401949e-05</v>
+        <v>3.697062401949002e-05</v>
       </c>
       <c r="BX5" t="n">
         <v>0.00184495615480462</v>
@@ -2686,7 +2686,7 @@
         <v>0.0002640283468310355</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0004957776840081842</v>
+        <v>0.0004957776840081843</v>
       </c>
       <c r="CC5" t="n">
         <v>0.000179391539757357</v>
@@ -2713,7 +2713,7 @@
         <v>0.01769684819762537</v>
       </c>
       <c r="CK5" t="n">
-        <v>5.179541767397701e-05</v>
+        <v>5.1795417673977e-05</v>
       </c>
       <c r="CL5" t="n">
         <v>0.00163765119331058</v>
@@ -2722,7 +2722,7 @@
         <v>5.740158734129223e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0004202960483021875</v>
+        <v>0.0004202960483021874</v>
       </c>
       <c r="CO5" t="n">
         <v>0.0006214515755795044</v>
@@ -2752,7 +2752,7 @@
         <v>0.0004599818491270817</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.004384914522418451</v>
+        <v>0.00438491452241845</v>
       </c>
       <c r="CY5" t="n">
         <v>0.0002150730033617087</v>
@@ -2770,7 +2770,7 @@
         <v>5.857288491736612e-05</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.002751110538380999</v>
+        <v>0.002751110538380998</v>
       </c>
       <c r="DE5" t="n">
         <v>0.0001704999385044117</v>
@@ -2797,7 +2797,7 @@
         <v>0.0003996388737403179</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0007959779737154493</v>
+        <v>0.0007959779737154494</v>
       </c>
       <c r="DN5" t="n">
         <v>5.169619128614461e-05</v>
@@ -2806,7 +2806,7 @@
         <v>0.002316521724466292</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.08445236644989626</v>
+        <v>0.08445236644989623</v>
       </c>
       <c r="DQ5" t="n">
         <v>3.332754700192381e-05</v>
@@ -2815,7 +2815,7 @@
         <v>0.0001345369836537669</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.001932563888200514</v>
+        <v>0.001932563888200513</v>
       </c>
       <c r="DT5" t="n">
         <v>0.001494898689947722</v>
@@ -2839,16 +2839,16 @@
         <v>0.0004475105507908678</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0005282043478935818</v>
+        <v>0.0005282043478935819</v>
       </c>
       <c r="EB5" t="n">
         <v>0.0005431212089902845</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.01365944088563638</v>
+        <v>0.01365944088563639</v>
       </c>
       <c r="ED5" t="n">
-        <v>3.645284754399209e-05</v>
+        <v>3.645284754399208e-05</v>
       </c>
       <c r="EE5" t="n">
         <v>0.0001321895673715872</v>
@@ -2857,7 +2857,7 @@
         <v>2.301894193843465e-05</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0003162716753798484</v>
+        <v>0.0003162716753798483</v>
       </c>
       <c r="EH5" t="n">
         <v>0.0001433828800304166</v>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3559765301098402</v>
+        <v>0.3559765301098404</v>
       </c>
       <c r="C6" t="n">
         <v>0.001378754660338261</v>
@@ -2899,13 +2899,13 @@
         <v>0.03567966981741302</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1744910764837267</v>
+        <v>0.1744910764837265</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4940064743003992</v>
+        <v>0.4940064743004003</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1679976866198874</v>
+        <v>0.1679976866198876</v>
       </c>
       <c r="I6" t="n">
         <v>0.01264695214450926</v>
@@ -2917,13 +2917,13 @@
         <v>0.0099903095590981</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0514161297290008</v>
+        <v>0.05141612972900081</v>
       </c>
       <c r="M6" t="n">
         <v>0.01274488917665001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0182906118942867</v>
+        <v>0.01829061189428671</v>
       </c>
       <c r="O6" t="n">
         <v>0.002230850150217093</v>
@@ -2932,13 +2932,13 @@
         <v>0.01203040614552389</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01193188947996321</v>
+        <v>0.003062825305500852</v>
       </c>
       <c r="R6" t="n">
         <v>0.007525443789274805</v>
       </c>
       <c r="S6" t="n">
-        <v>0.006695000836577084</v>
+        <v>0.006695000836577082</v>
       </c>
       <c r="T6" t="n">
         <v>0.02220033555120176</v>
@@ -2947,7 +2947,7 @@
         <v>0.0001309160543681167</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001875320753339351</v>
+        <v>0.00187532075333935</v>
       </c>
       <c r="W6" t="n">
         <v>0.01371662130681589</v>
@@ -2956,10 +2956,10 @@
         <v>0.0002343108480085284</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003216228101358316</v>
+        <v>0.003216228101358317</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.005496532609139634</v>
+        <v>0.005496532609139635</v>
       </c>
       <c r="AA6" t="n">
         <v>0.01816839068838072</v>
@@ -2968,7 +2968,7 @@
         <v>0.001324056773634768</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06363532686346257</v>
+        <v>0.06363532686346259</v>
       </c>
       <c r="AD6" t="n">
         <v>6.798486235701442e-05</v>
@@ -2977,10 +2977,10 @@
         <v>3.295747315510672e-05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.04993537163229203</v>
+        <v>0.04993537163229205</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.02310378264756587</v>
+        <v>0.02310378264756585</v>
       </c>
       <c r="AH6" t="n">
         <v>0.002701862619500335</v>
@@ -2992,13 +2992,13 @@
         <v>0.002978688723026406</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.02018352660108585</v>
+        <v>0.02018352660108584</v>
       </c>
       <c r="AL6" t="n">
         <v>0.001838557028409628</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0003613415606113761</v>
+        <v>0.0003613415606113759</v>
       </c>
       <c r="AN6" t="n">
         <v>0.0002604996700505414</v>
@@ -3010,7 +3010,7 @@
         <v>0.001026413051192482</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.002779624886213803</v>
+        <v>0.002779624886213802</v>
       </c>
       <c r="AR6" t="n">
         <v>0.006354516559533596</v>
@@ -3028,25 +3028,25 @@
         <v>0.001980674329669163</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.02241232913517603</v>
+        <v>0.02241232913517602</v>
       </c>
       <c r="AX6" t="n">
         <v>0.001384046987299332</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.04489240818612222</v>
+        <v>0.04489240818612219</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.0007018822935937685</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0003186355394198097</v>
+        <v>0.0003186355394198096</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.03367427063012115</v>
+        <v>0.03367427063012116</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.01081800145282346</v>
+        <v>0.01081800145282347</v>
       </c>
       <c r="BD6" t="n">
         <v>0.01822907967396244</v>
@@ -3064,7 +3064,7 @@
         <v>0.01041476992454605</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0005027518917166845</v>
+        <v>0.0005027518917166843</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.0008046071679185987</v>
@@ -3076,31 +3076,31 @@
         <v>0.000167141058022837</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.03081010986303456</v>
+        <v>0.03081010986303457</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.002097987241980924</v>
+        <v>0.002097987241980925</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0001082506515395765</v>
+        <v>0.0001082506515395764</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0005140636186815318</v>
+        <v>0.0005140636186815319</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0006196285052672797</v>
+        <v>0.0006196285052672798</v>
       </c>
       <c r="BR6" t="n">
         <v>0.001064059459121359</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.01208401859459659</v>
+        <v>0.0120840185945966</v>
       </c>
       <c r="BT6" t="n">
         <v>0.00544692458977884</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.005482678624033167</v>
+        <v>0.005482678624033165</v>
       </c>
       <c r="BV6" t="n">
         <v>0.00392118439658188</v>
@@ -3166,7 +3166,7 @@
         <v>0.001001575197170887</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.001568767608760131</v>
+        <v>0.00156876760876013</v>
       </c>
       <c r="CR6" t="n">
         <v>0.0004615693796872052</v>
@@ -3175,7 +3175,7 @@
         <v>0.0001819757669853316</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.000593602486061329</v>
+        <v>0.0005936024860613289</v>
       </c>
       <c r="CU6" t="n">
         <v>0.0004107815422950545</v>
@@ -3202,7 +3202,7 @@
         <v>0.0006971741063490495</v>
       </c>
       <c r="DC6" t="n">
-        <v>6.205004268631076e-05</v>
+        <v>6.205004268631075e-05</v>
       </c>
       <c r="DD6" t="n">
         <v>0.002628277102049681</v>
@@ -3232,7 +3232,7 @@
         <v>0.0003452849446034507</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.000406288288233853</v>
+        <v>0.0004062882882338531</v>
       </c>
       <c r="DN6" t="n">
         <v>5.043319776536446e-05</v>
@@ -3241,7 +3241,7 @@
         <v>0.002871800361490551</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.09333327011157896</v>
+        <v>0.09333327011157902</v>
       </c>
       <c r="DQ6" t="n">
         <v>3.7114469739886e-05</v>
@@ -3268,16 +3268,16 @@
         <v>0.001106492855203367</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0002317177684017594</v>
+        <v>0.0002317177684017595</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0004649150703924182</v>
+        <v>0.0004649150703924183</v>
       </c>
       <c r="EA6" t="n">
         <v>0.0005706064108255011</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0005018882575982627</v>
+        <v>0.0005018882575982626</v>
       </c>
       <c r="EC6" t="n">
         <v>0.0150829067750236</v>
@@ -3286,7 +3286,7 @@
         <v>3.726243808945049e-05</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0001915844310053861</v>
+        <v>0.000191584431005386</v>
       </c>
       <c r="EF6" t="n">
         <v>2.596265060458387e-05</v>
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3616973321520131</v>
+        <v>0.3616973321520129</v>
       </c>
       <c r="C7" t="n">
         <v>0.001373063284887813</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001848820701685509</v>
+        <v>0.001848820701685508</v>
       </c>
       <c r="E7" t="n">
         <v>0.03844697540226989</v>
@@ -3337,10 +3337,10 @@
         <v>0.1697021620370526</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4892953541991784</v>
+        <v>0.4892953541991773</v>
       </c>
       <c r="H7" t="n">
-        <v>0.179113754026307</v>
+        <v>0.1791137540263069</v>
       </c>
       <c r="I7" t="n">
         <v>0.01411219186966198</v>
@@ -3349,13 +3349,13 @@
         <v>0.03359434022454191</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01080203807826755</v>
+        <v>0.01080203807826756</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05173207640148288</v>
+        <v>0.05173207640148293</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01242772029022885</v>
+        <v>0.01242772029022884</v>
       </c>
       <c r="N7" t="n">
         <v>0.0188585863509152</v>
@@ -3367,7 +3367,7 @@
         <v>0.01179702216080809</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01186449058438758</v>
+        <v>0.003151882828460583</v>
       </c>
       <c r="R7" t="n">
         <v>0.00747835788304578</v>
@@ -3376,7 +3376,7 @@
         <v>0.006877918622446228</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02338085889977005</v>
+        <v>0.02338085889977004</v>
       </c>
       <c r="U7" t="n">
         <v>0.0001538682995691823</v>
@@ -3394,10 +3394,10 @@
         <v>0.003366688965504633</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00533698693103664</v>
+        <v>0.005336986931036639</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01965903042866259</v>
+        <v>0.0196590304286626</v>
       </c>
       <c r="AB7" t="n">
         <v>0.001390744191897979</v>
@@ -3409,7 +3409,7 @@
         <v>6.68060488343329e-05</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.439757481255417e-05</v>
+        <v>3.439757481255416e-05</v>
       </c>
       <c r="AF7" t="n">
         <v>0.05220280695474431</v>
@@ -3418,13 +3418,13 @@
         <v>0.02486465547451934</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.002841832303589513</v>
+        <v>0.002841832303589514</v>
       </c>
       <c r="AI7" t="n">
         <v>0.0009428694351277463</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.003084699840287304</v>
+        <v>0.003084699840287305</v>
       </c>
       <c r="AK7" t="n">
         <v>0.02083896394982996</v>
@@ -3439,7 +3439,7 @@
         <v>0.0002934227635793438</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.001416755716535366</v>
+        <v>0.001416755716535365</v>
       </c>
       <c r="AP7" t="n">
         <v>0.00105091078212547</v>
@@ -3481,10 +3481,10 @@
         <v>0.03538229842722888</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0120307657836993</v>
+        <v>0.01203076578369929</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01806060978014848</v>
+        <v>0.01806060978014847</v>
       </c>
       <c r="BE7" t="n">
         <v>0.001479733313999956</v>
@@ -3496,10 +3496,10 @@
         <v>0.001911367862094573</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.009933543160497391</v>
+        <v>0.009933543160497398</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0006074986122925703</v>
+        <v>0.0006074986122925704</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.0007362143741839885</v>
@@ -3511,16 +3511,16 @@
         <v>0.0001859488650466923</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03060931199534069</v>
+        <v>0.0306093119953407</v>
       </c>
       <c r="BN7" t="n">
         <v>0.002149051774726496</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.000102852443070222</v>
+        <v>0.0001028524430702221</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0005300158437942502</v>
+        <v>0.0005300158437942501</v>
       </c>
       <c r="BQ7" t="n">
         <v>0.0007129157404086203</v>
@@ -3529,7 +3529,7 @@
         <v>0.0008685513261982774</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.01131553973951998</v>
+        <v>0.01131553973951997</v>
       </c>
       <c r="BT7" t="n">
         <v>0.006030814723802178</v>
@@ -3538,10 +3538,10 @@
         <v>0.005779390718946253</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.004192245394739304</v>
+        <v>0.004192245394739303</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.855590830866798e-05</v>
+        <v>3.855590830866796e-05</v>
       </c>
       <c r="BX7" t="n">
         <v>0.001839795264559137</v>
@@ -3559,10 +3559,10 @@
         <v>0.0004179813924042926</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0001741180367564558</v>
+        <v>0.0001741180367564559</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0004183774307009281</v>
+        <v>0.0004183774307009282</v>
       </c>
       <c r="CE7" t="n">
         <v>0.008195495978784103</v>
@@ -3571,7 +3571,7 @@
         <v>0.001070142199452228</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.009290908223826779</v>
+        <v>0.009290908223826786</v>
       </c>
       <c r="CH7" t="n">
         <v>0.0009083841108493771</v>
@@ -3637,7 +3637,7 @@
         <v>0.0007196871644634076</v>
       </c>
       <c r="DC7" t="n">
-        <v>5.403472683014232e-05</v>
+        <v>5.403472683014233e-05</v>
       </c>
       <c r="DD7" t="n">
         <v>0.002573017598439096</v>
@@ -3658,10 +3658,10 @@
         <v>0.000118402532937222</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0002917978935498036</v>
+        <v>0.0002917978935498035</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.002323168031998053</v>
+        <v>0.002323168031998054</v>
       </c>
       <c r="DL7" t="n">
         <v>0.000351560958075553</v>
@@ -3673,7 +3673,7 @@
         <v>4.921790980357102e-05</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.003004758354095035</v>
+        <v>0.003004758354095033</v>
       </c>
       <c r="DP7" t="n">
         <v>0.09697002307929983</v>
@@ -3706,7 +3706,7 @@
         <v>0.0002381647365952744</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0004772926348514086</v>
+        <v>0.0004772926348514087</v>
       </c>
       <c r="EA7" t="n">
         <v>0.0005397737928616774</v>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3614780161646687</v>
+        <v>0.361478016164669</v>
       </c>
       <c r="C8" t="n">
         <v>0.001392408343939392</v>
@@ -3769,10 +3769,10 @@
         <v>0.04232931537698223</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1705288408211067</v>
+        <v>0.1705288408211066</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5010929176068748</v>
+        <v>0.5010929176068742</v>
       </c>
       <c r="H8" t="n">
         <v>0.1819542757754737</v>
@@ -3787,7 +3787,7 @@
         <v>0.01053657061366469</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05233916209310854</v>
+        <v>0.05233916209310856</v>
       </c>
       <c r="M8" t="n">
         <v>0.01297969573764256</v>
@@ -3802,16 +3802,16 @@
         <v>0.01239050887528845</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01254175934502911</v>
+        <v>0.003123697486757893</v>
       </c>
       <c r="R8" t="n">
-        <v>0.007240553950184897</v>
+        <v>0.007240553950184899</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00676906830287393</v>
+        <v>0.006769068302873928</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02124143526100869</v>
+        <v>0.02124143526100867</v>
       </c>
       <c r="U8" t="n">
         <v>0.0001578248243646006</v>
@@ -3832,7 +3832,7 @@
         <v>0.005199178536030591</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01977961876595256</v>
+        <v>0.01977961876595257</v>
       </c>
       <c r="AB8" t="n">
         <v>0.001389534465788636</v>
@@ -3841,19 +3841,19 @@
         <v>0.06018014540871497</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.577213690896522e-05</v>
+        <v>6.577213690896524e-05</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.472726258442439e-05</v>
+        <v>3.472726258442438e-05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.05086223609404431</v>
+        <v>0.05086223609404426</v>
       </c>
       <c r="AG8" t="n">
         <v>0.02564636239593393</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.002883643667024358</v>
+        <v>0.002883643667024356</v>
       </c>
       <c r="AI8" t="n">
         <v>0.001036791363592649</v>
@@ -3877,19 +3877,19 @@
         <v>0.001429652514494395</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001082806094958201</v>
+        <v>0.0010828060949582</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.003052100109383908</v>
+        <v>0.00305210010938391</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.006515197046603005</v>
+        <v>0.006515197046603008</v>
       </c>
       <c r="AS8" t="n">
         <v>6.218673563640139e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0003130146929285172</v>
+        <v>0.0003130146929285173</v>
       </c>
       <c r="AU8" t="n">
         <v>0.0003912377863052071</v>
@@ -3898,19 +3898,19 @@
         <v>0.002304125484376717</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.02235164912643411</v>
+        <v>0.02235164912643412</v>
       </c>
       <c r="AX8" t="n">
         <v>0.001308024757167531</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.04219469786854745</v>
+        <v>0.04219469786854742</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.000851541092791218</v>
+        <v>0.0008515410927912178</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.000300305932204428</v>
+        <v>0.0003003059322044278</v>
       </c>
       <c r="BB8" t="n">
         <v>0.03763131538072371</v>
@@ -3934,13 +3934,13 @@
         <v>0.01072106038231166</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0006638297347294063</v>
+        <v>0.0006638297347294061</v>
       </c>
       <c r="BJ8" t="n">
         <v>0.0006426347094806681</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.009763937830748453</v>
+        <v>0.009763937830748456</v>
       </c>
       <c r="BL8" t="n">
         <v>0.0001811579619540046</v>
@@ -3967,7 +3967,7 @@
         <v>0.01238580143779191</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.005233142608453797</v>
+        <v>0.005233142608453798</v>
       </c>
       <c r="BU8" t="n">
         <v>0.005647507973007072</v>
@@ -3988,7 +3988,7 @@
         <v>0.02996290848989883</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0002572270552155944</v>
+        <v>0.0002572270552155942</v>
       </c>
       <c r="CB8" t="n">
         <v>0.0004538736245372539</v>
@@ -4006,7 +4006,7 @@
         <v>0.001144905449238564</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.009912847070386942</v>
+        <v>0.00991284707038694</v>
       </c>
       <c r="CH8" t="n">
         <v>0.0009938693279002105</v>
@@ -4024,7 +4024,7 @@
         <v>0.001504917865565166</v>
       </c>
       <c r="CM8" t="n">
-        <v>5.576607935225831e-05</v>
+        <v>5.576607935225832e-05</v>
       </c>
       <c r="CN8" t="n">
         <v>0.0004046873963303452</v>
@@ -4051,7 +4051,7 @@
         <v>0.0002985838899769202</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0006579207718063881</v>
+        <v>0.000657920771806388</v>
       </c>
       <c r="CW8" t="n">
         <v>0.0004264881422646655</v>
@@ -4060,7 +4060,7 @@
         <v>0.004346914828000808</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0002165559912580432</v>
+        <v>0.0002165559912580433</v>
       </c>
       <c r="CZ8" t="n">
         <v>0.0004990178664701329</v>
@@ -4072,7 +4072,7 @@
         <v>0.0007910649998152807</v>
       </c>
       <c r="DC8" t="n">
-        <v>6.303864519331281e-05</v>
+        <v>6.303864519331283e-05</v>
       </c>
       <c r="DD8" t="n">
         <v>0.002794799753451129</v>
@@ -4111,7 +4111,7 @@
         <v>0.0025586432033828</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0941982643927097</v>
+        <v>0.09419826439270973</v>
       </c>
       <c r="DQ8" t="n">
         <v>3.148659225065586e-05</v>
@@ -4120,7 +4120,7 @@
         <v>0.0001217149295216939</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.001966066983778735</v>
+        <v>0.001966066983778737</v>
       </c>
       <c r="DT8" t="n">
         <v>0.001536057013027726</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3697712239747259</v>
+        <v>0.3697712239747263</v>
       </c>
       <c r="C9" t="n">
         <v>0.001461218296793041</v>
@@ -4207,7 +4207,7 @@
         <v>0.1843521940566766</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4920509336778491</v>
+        <v>0.4920509336778487</v>
       </c>
       <c r="H9" t="n">
         <v>0.1950488683076636</v>
@@ -4222,28 +4222,28 @@
         <v>0.01328018374486239</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05318966227280729</v>
+        <v>0.05318966227280726</v>
       </c>
       <c r="M9" t="n">
         <v>0.01277366436307569</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02065614185206345</v>
+        <v>0.02065614185206344</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002802238496253391</v>
+        <v>0.002802238496253389</v>
       </c>
       <c r="P9" t="n">
         <v>0.01184068921238392</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01258368884567358</v>
+        <v>0.003158750871643139</v>
       </c>
       <c r="R9" t="n">
-        <v>0.007613628872687187</v>
+        <v>0.007613628872687188</v>
       </c>
       <c r="S9" t="n">
-        <v>0.007257440205810478</v>
+        <v>0.007257440205810479</v>
       </c>
       <c r="T9" t="n">
         <v>0.02271422063637896</v>
@@ -4264,7 +4264,7 @@
         <v>0.003511619059138761</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.005149533606936167</v>
+        <v>0.005149533606936168</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01766204664759897</v>
@@ -4273,7 +4273,7 @@
         <v>0.001358423529721423</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.06014760232327254</v>
+        <v>0.0601476023232725</v>
       </c>
       <c r="AD9" t="n">
         <v>6.346753345277737e-05</v>
@@ -4288,16 +4288,16 @@
         <v>0.03365168707637019</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.003034295259340325</v>
+        <v>0.003034295259340324</v>
       </c>
       <c r="AI9" t="n">
         <v>0.001124817482863579</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.002930978928564623</v>
+        <v>0.002930978928564624</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01972568503579263</v>
+        <v>0.01972568503579264</v>
       </c>
       <c r="AL9" t="n">
         <v>0.001748338111495326</v>
@@ -4309,7 +4309,7 @@
         <v>0.0003190562087911122</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001598223016039848</v>
+        <v>0.001598223016039847</v>
       </c>
       <c r="AP9" t="n">
         <v>0.001191754414735129</v>
@@ -4318,7 +4318,7 @@
         <v>0.00381278888731524</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.006423593791213471</v>
+        <v>0.006423593791213469</v>
       </c>
       <c r="AS9" t="n">
         <v>6.268828405107488e-05</v>
@@ -4336,19 +4336,19 @@
         <v>0.0191317771403957</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001228198512256291</v>
+        <v>0.001228198512256292</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.03684657679507462</v>
+        <v>0.03684657679507464</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.0007781084740626549</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0002905291856727269</v>
+        <v>0.000290529185672727</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.04149039456243862</v>
+        <v>0.04149039456243861</v>
       </c>
       <c r="BC9" t="n">
         <v>0.0137420391066276</v>
@@ -4363,13 +4363,13 @@
         <v>0.001753233341142003</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001841532175809908</v>
+        <v>0.001841532175809906</v>
       </c>
       <c r="BH9" t="n">
         <v>0.01047524794068949</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.000722373676153161</v>
+        <v>0.0007223736761531612</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.0006070397836695424</v>
@@ -4402,13 +4402,13 @@
         <v>0.01335947588725805</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.005462692860165885</v>
+        <v>0.005462692860165888</v>
       </c>
       <c r="BU9" t="n">
         <v>0.00605342333201403</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.004803932777355969</v>
+        <v>0.00480393277735597</v>
       </c>
       <c r="BW9" t="n">
         <v>4.447498595534028e-05</v>
@@ -4417,7 +4417,7 @@
         <v>0.001812307112114946</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0005548065921564987</v>
+        <v>0.0005548065921564988</v>
       </c>
       <c r="BZ9" t="n">
         <v>0.0293935148874305</v>
@@ -4441,7 +4441,7 @@
         <v>0.001223363094285114</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.009908652944542122</v>
+        <v>0.009908652944542126</v>
       </c>
       <c r="CH9" t="n">
         <v>0.0009286692539576117</v>
@@ -4471,7 +4471,7 @@
         <v>0.0008288201338415135</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001400752757600808</v>
+        <v>0.001400752757600807</v>
       </c>
       <c r="CR9" t="n">
         <v>0.0005052977084871318</v>
@@ -4498,7 +4498,7 @@
         <v>0.0002091924317925715</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0005071225865893232</v>
+        <v>0.0005071225865893231</v>
       </c>
       <c r="DA9" t="n">
         <v>0.001072238823430902</v>
@@ -4531,13 +4531,13 @@
         <v>0.0002794959528960382</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.002283419087144216</v>
+        <v>0.002283419087144218</v>
       </c>
       <c r="DL9" t="n">
         <v>0.0004051911585836952</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0009101288271652708</v>
+        <v>0.000910128827165271</v>
       </c>
       <c r="DN9" t="n">
         <v>4.867918625146371e-05</v>
@@ -4546,7 +4546,7 @@
         <v>0.002485268533908817</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.08211157920822962</v>
+        <v>0.08211157920822963</v>
       </c>
       <c r="DQ9" t="n">
         <v>3.164482429812269e-05</v>
@@ -4576,7 +4576,7 @@
         <v>0.0002317235700291241</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0004473471999959774</v>
+        <v>0.0004473471999959775</v>
       </c>
       <c r="EA9" t="n">
         <v>0.00050592800725357</v>

--- a/data/proteomics/organell_protein_ratio_tao2.xlsx
+++ b/data/proteomics/organell_protein_ratio_tao2.xlsx
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3768291948768152</v>
+        <v>0.3768291948768154</v>
       </c>
       <c r="C2" t="n">
         <v>0.001132151698543643</v>
@@ -1159,16 +1159,16 @@
         <v>0.02796931597783909</v>
       </c>
       <c r="F2" t="n">
-        <v>0.144285181020711</v>
+        <v>0.1442851810207112</v>
       </c>
       <c r="G2" t="n">
         <v>0.5368318577506769</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1533902428867231</v>
+        <v>0.153390242886723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00982076731278198</v>
+        <v>0.009820767312781985</v>
       </c>
       <c r="J2" t="n">
         <v>0.01929128761908306</v>
@@ -1177,10 +1177,10 @@
         <v>0.007411843722660433</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03923806603228645</v>
+        <v>0.03923806603228647</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00387474670006303</v>
+        <v>0.003874746700063031</v>
       </c>
       <c r="N2" t="n">
         <v>0.01658881084334536</v>
@@ -1189,7 +1189,7 @@
         <v>0.003241068740903495</v>
       </c>
       <c r="P2" t="n">
-        <v>0.008583817677694554</v>
+        <v>0.008583817677694559</v>
       </c>
       <c r="Q2" t="n">
         <v>0.002597669596774738</v>
@@ -1207,7 +1207,7 @@
         <v>7.584595539100256e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00139544937292067</v>
+        <v>0.001395449372920671</v>
       </c>
       <c r="W2" t="n">
         <v>0.01421551377485446</v>
@@ -1222,7 +1222,7 @@
         <v>0.004488893708375062</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.02035291544636118</v>
+        <v>0.0203529154463612</v>
       </c>
       <c r="AB2" t="n">
         <v>0.00110025581645589</v>
@@ -1234,22 +1234,22 @@
         <v>6.293266183093604e-05</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.879704407604192e-05</v>
+        <v>2.879704407604193e-05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.04640565340505702</v>
+        <v>0.04640565340505703</v>
       </c>
       <c r="AG2" t="n">
         <v>0.0182294097391866</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.002497131950886001</v>
+        <v>0.002497131950886</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0007245952945119374</v>
+        <v>0.0007245952945119369</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.002523246809566363</v>
+        <v>0.002523246809566364</v>
       </c>
       <c r="AK2" t="n">
         <v>0.01770357406143309</v>
@@ -1264,7 +1264,7 @@
         <v>0.0001879706679759903</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.001038116023557726</v>
+        <v>0.001038116023557725</v>
       </c>
       <c r="AP2" t="n">
         <v>0.0007866918669784848</v>
@@ -1279,7 +1279,7 @@
         <v>4.220551426200235e-05</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0002213542464594871</v>
+        <v>0.0002213542464594872</v>
       </c>
       <c r="AU2" t="n">
         <v>0.0002778650873692981</v>
@@ -1294,28 +1294,28 @@
         <v>0.001782223229634296</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.05110038990234936</v>
+        <v>0.05110038990234938</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0005147931182266695</v>
+        <v>0.0005147931182266694</v>
       </c>
       <c r="BA2" t="n">
         <v>0.0002646001060258182</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.02645251988049442</v>
+        <v>0.02645251988049443</v>
       </c>
       <c r="BC2" t="n">
         <v>0.008850125841367145</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.01620130379704648</v>
+        <v>0.01620130379704647</v>
       </c>
       <c r="BE2" t="n">
         <v>0.001190273228478583</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.001260923307931317</v>
+        <v>0.001260923307931316</v>
       </c>
       <c r="BG2" t="n">
         <v>0.001815631860843193</v>
@@ -1330,7 +1330,7 @@
         <v>0.00100276485049489</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.0074652230456123</v>
+        <v>0.007465223045612305</v>
       </c>
       <c r="BL2" t="n">
         <v>0.0001385114071495396</v>
@@ -1339,16 +1339,16 @@
         <v>0.0602992669928927</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.001855642594870616</v>
+        <v>0.001855642594870617</v>
       </c>
       <c r="BO2" t="n">
         <v>7.30955997707067e-05</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0003739942490058976</v>
+        <v>0.0003739942490058977</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0004997864183314714</v>
+        <v>0.0004997864183314712</v>
       </c>
       <c r="BR2" t="n">
         <v>0.0008606046001677174</v>
@@ -1372,7 +1372,7 @@
         <v>0.001572969846242717</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0004691766294853186</v>
+        <v>0.0004691766294853187</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.0004915161852386597</v>
@@ -1393,7 +1393,7 @@
         <v>0.003082195542483827</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.000499234832510476</v>
+        <v>0.0004992348325104761</v>
       </c>
       <c r="CG2" t="n">
         <v>0.001405378873281455</v>
@@ -1402,7 +1402,7 @@
         <v>0.0006278762246342473</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0001034318234018773</v>
+        <v>0.0001034318234018772</v>
       </c>
       <c r="CJ2" t="n">
         <v>0.002485336189261843</v>
@@ -1429,7 +1429,7 @@
         <v>0.002304618940482489</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.0004943506417664812</v>
+        <v>0.0004943506417664813</v>
       </c>
       <c r="CS2" t="n">
         <v>0.0001997123109852517</v>
@@ -1459,10 +1459,10 @@
         <v>0.0004433886338713066</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0004975938997294174</v>
+        <v>0.0004975938997294175</v>
       </c>
       <c r="DC2" t="n">
-        <v>5.067118891863229e-05</v>
+        <v>5.06711889186323e-05</v>
       </c>
       <c r="DD2" t="n">
         <v>0.002331094335395748</v>
@@ -1498,13 +1498,13 @@
         <v>4.970591443250374e-05</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.00244461281526292</v>
+        <v>0.002444612815262921</v>
       </c>
       <c r="DP2" t="n">
         <v>0.1055178157988777</v>
       </c>
       <c r="DQ2" t="n">
-        <v>4.450243659230129e-05</v>
+        <v>4.45024365923013e-05</v>
       </c>
       <c r="DR2" t="n">
         <v>0.0001060098233812161</v>
@@ -1516,7 +1516,7 @@
         <v>0.001710345021070071</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.002701557053497846</v>
+        <v>0.002701557053497847</v>
       </c>
       <c r="DV2" t="n">
         <v>0.0007960260391395138</v>
@@ -1531,13 +1531,13 @@
         <v>0.0002151997034669004</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.0004861730729641608</v>
+        <v>0.0004861730729641607</v>
       </c>
       <c r="EA2" t="n">
         <v>0.0006716585259983622</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.0004413261305732982</v>
+        <v>0.0004413261305732981</v>
       </c>
       <c r="EC2" t="n">
         <v>0.01381315986830695</v>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3804552307818095</v>
+        <v>0.3804552307818093</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00132016033506342</v>
+        <v>0.001320160335063421</v>
       </c>
       <c r="D3" t="n">
         <v>0.001627248963576847</v>
@@ -1600,10 +1600,10 @@
         <v>0.5222899840034256</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1693695005601436</v>
+        <v>0.1693695005601437</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01272541058396213</v>
+        <v>0.01272541058396212</v>
       </c>
       <c r="J3" t="n">
         <v>0.01966881702894218</v>
@@ -1627,7 +1627,7 @@
         <v>0.009424272656281605</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002967647280086907</v>
+        <v>0.002967647280086905</v>
       </c>
       <c r="R3" t="n">
         <v>0.006671524409867072</v>
@@ -1654,25 +1654,25 @@
         <v>0.003060109610215864</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.004886034659579245</v>
+        <v>0.004886034659579246</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02031016049953764</v>
+        <v>0.02031016049953763</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001205469589752735</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.03054085609221922</v>
+        <v>0.03054085609221923</v>
       </c>
       <c r="AD3" t="n">
         <v>6.696160691778797e-05</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.934383533903403e-05</v>
+        <v>2.934383533903402e-05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.04963455621733457</v>
+        <v>0.04963455621733455</v>
       </c>
       <c r="AG3" t="n">
         <v>0.01798793815324417</v>
@@ -1738,13 +1738,13 @@
         <v>0.0002903848586063492</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.02658187400978724</v>
+        <v>0.02658187400978723</v>
       </c>
       <c r="BC3" t="n">
         <v>0.00999353554726848</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.01822466964201763</v>
+        <v>0.01822466964201762</v>
       </c>
       <c r="BE3" t="n">
         <v>0.001353716991249518</v>
@@ -1753,7 +1753,7 @@
         <v>0.00140404096750241</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.001896704520613368</v>
+        <v>0.001896704520613367</v>
       </c>
       <c r="BH3" t="n">
         <v>0.006241537166703641</v>
@@ -1765,13 +1765,13 @@
         <v>0.0009260455711801003</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.007775798796547776</v>
+        <v>0.00777579879654777</v>
       </c>
       <c r="BL3" t="n">
         <v>0.0001406156704372236</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.05387226637965809</v>
+        <v>0.05387226637965814</v>
       </c>
       <c r="BN3" t="n">
         <v>0.001986899811004473</v>
@@ -1801,10 +1801,10 @@
         <v>0.003520903378598084</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.407117380451333e-05</v>
+        <v>3.407117380451332e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.001690431604393317</v>
+        <v>0.001690431604393316</v>
       </c>
       <c r="BY3" t="n">
         <v>0.000516797247994945</v>
@@ -1813,7 +1813,7 @@
         <v>0.0007644590009047</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0002561006000009095</v>
+        <v>0.0002561006000009094</v>
       </c>
       <c r="CB3" t="n">
         <v>0.0003200079468116968</v>
@@ -1828,13 +1828,13 @@
         <v>0.003503851982076092</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0005077509927878699</v>
+        <v>0.00050775099278787</v>
       </c>
       <c r="CG3" t="n">
         <v>0.001454561139994631</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0006963491138195203</v>
+        <v>0.0006963491138195207</v>
       </c>
       <c r="CI3" t="n">
         <v>0.0001810762156735534</v>
@@ -1852,7 +1852,7 @@
         <v>9.04995010675067e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0003481258199929592</v>
+        <v>0.0003481258199929593</v>
       </c>
       <c r="CO3" t="n">
         <v>0.0006154903742604358</v>
@@ -1879,7 +1879,7 @@
         <v>0.0005456713944872538</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.0004382614322503935</v>
+        <v>0.0004382614322503936</v>
       </c>
       <c r="CX3" t="n">
         <v>0.003645925939561363</v>
@@ -1888,7 +1888,7 @@
         <v>0.0002390565046032459</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0004802966045816088</v>
+        <v>0.0004802966045816089</v>
       </c>
       <c r="DA3" t="n">
         <v>0.0005542242477225194</v>
@@ -1915,7 +1915,7 @@
         <v>0.001297000689122298</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0001124531725752535</v>
+        <v>0.0001124531725752536</v>
       </c>
       <c r="DJ3" t="n">
         <v>0.0002316727406636153</v>
@@ -1936,7 +1936,7 @@
         <v>0.00264243668205822</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.09930926869169567</v>
+        <v>0.09930926869169562</v>
       </c>
       <c r="DQ3" t="n">
         <v>4.699815490971136e-05</v>
@@ -1951,7 +1951,7 @@
         <v>0.001612710619804918</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.003101319975647466</v>
+        <v>0.003101319975647465</v>
       </c>
       <c r="DV3" t="n">
         <v>0.0008286101250379598</v>
@@ -1963,13 +1963,13 @@
         <v>0.001096141118452706</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0002173562248200256</v>
+        <v>0.0002173562248200255</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0005407231574283842</v>
+        <v>0.0005407231574283848</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0006086407349358788</v>
+        <v>0.0006086407349358792</v>
       </c>
       <c r="EB3" t="n">
         <v>0.0004870411957452499</v>
@@ -2017,25 +2017,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3478653282155376</v>
+        <v>0.3478653282155383</v>
       </c>
       <c r="C4" t="n">
         <v>0.0008980883803972595</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001438385200101837</v>
+        <v>0.001438385200101838</v>
       </c>
       <c r="E4" t="n">
         <v>0.03877560203496943</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1698939931202434</v>
+        <v>0.1698939931202437</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5249719239761556</v>
+        <v>0.5249719239761549</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1828454858289217</v>
+        <v>0.1828454858289216</v>
       </c>
       <c r="I4" t="n">
         <v>0.01345188497120252</v>
@@ -2047,10 +2047,10 @@
         <v>0.007864729814611686</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04206805331419958</v>
+        <v>0.04206805331419961</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009986372781839108</v>
+        <v>0.009986372781839111</v>
       </c>
       <c r="N4" t="n">
         <v>0.02048900088668536</v>
@@ -2059,19 +2059,19 @@
         <v>0.003003126477312455</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01014578246298563</v>
+        <v>0.01014578246298564</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002421776729006168</v>
+        <v>0.002421776729006169</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005376242919750383</v>
+        <v>0.005376242919750388</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005759177726387769</v>
+        <v>0.005759177726387767</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01614518379096858</v>
+        <v>0.01614518379096859</v>
       </c>
       <c r="U4" t="n">
         <v>9.894070994095339e-05</v>
@@ -2083,7 +2083,7 @@
         <v>0.01485365952847897</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001345536163977731</v>
+        <v>0.0001345536163977732</v>
       </c>
       <c r="Y4" t="n">
         <v>0.003671136370789009</v>
@@ -2092,16 +2092,16 @@
         <v>0.003649792913838155</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0228379792689909</v>
+        <v>0.02283797926899088</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009787961993763551</v>
+        <v>0.0009787961993763549</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0445651527588899</v>
+        <v>0.04456515275888988</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.85643728940809e-05</v>
+        <v>5.856437289408091e-05</v>
       </c>
       <c r="AE4" t="n">
         <v>3.576898887621034e-05</v>
@@ -2143,7 +2143,7 @@
         <v>0.004036960396779889</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005747501814919279</v>
+        <v>0.005747501814919278</v>
       </c>
       <c r="AS4" t="n">
         <v>5.473977402400768e-05</v>
@@ -2155,25 +2155,25 @@
         <v>0.000311801557710404</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002058821963646659</v>
+        <v>0.002058821963646658</v>
       </c>
       <c r="AW4" t="n">
         <v>0.033079410819841</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001246637522146828</v>
+        <v>0.001246637522146829</v>
       </c>
       <c r="AY4" t="n">
         <v>0.04596507698038794</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0007638482331707649</v>
+        <v>0.0007638482331707648</v>
       </c>
       <c r="BA4" t="n">
         <v>0.0002499117291670613</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.03527502634714922</v>
+        <v>0.03527502634714921</v>
       </c>
       <c r="BC4" t="n">
         <v>0.01281455888261207</v>
@@ -2191,19 +2191,19 @@
         <v>0.001743176370509748</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.01144270918895024</v>
+        <v>0.01144270918895025</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.000517838375505969</v>
+        <v>0.0005178383755059688</v>
       </c>
       <c r="BJ4" t="n">
         <v>0.0007753813946489298</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.008639747397040421</v>
+        <v>0.008639747397040423</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0002175626672361456</v>
+        <v>0.0002175626672361455</v>
       </c>
       <c r="BM4" t="n">
         <v>0.03190890305665485</v>
@@ -2221,7 +2221,7 @@
         <v>0.0008105205610947146</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.000729966529153786</v>
+        <v>0.0007299665291537859</v>
       </c>
       <c r="BS4" t="n">
         <v>0.01654198821245007</v>
@@ -2230,10 +2230,10 @@
         <v>0.004673272531431944</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.005168632514184036</v>
+        <v>0.005168632514184038</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.004577656477999605</v>
+        <v>0.004577656477999606</v>
       </c>
       <c r="BW4" t="n">
         <v>1.807812364412974e-05</v>
@@ -2305,7 +2305,7 @@
         <v>0.0001340264764468637</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.000540268010541946</v>
+        <v>0.0005402680105419461</v>
       </c>
       <c r="CU4" t="n">
         <v>0.0003620905417895445</v>
@@ -2335,7 +2335,7 @@
         <v>8.547531646824605e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.00327320929714435</v>
+        <v>0.003273209297144348</v>
       </c>
       <c r="DE4" t="n">
         <v>0.0001220740373146931</v>
@@ -2344,13 +2344,13 @@
         <v>0.001602013747778149</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.008938164135909423</v>
+        <v>0.008938164135909425</v>
       </c>
       <c r="DH4" t="n">
         <v>0.001343972693806654</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0001524322151069399</v>
+        <v>0.0001524322151069398</v>
       </c>
       <c r="DJ4" t="n">
         <v>0.0002470144626051505</v>
@@ -2365,7 +2365,7 @@
         <v>0.0005105808440493644</v>
       </c>
       <c r="DN4" t="n">
-        <v>5.483058513720899e-05</v>
+        <v>5.483058513720901e-05</v>
       </c>
       <c r="DO4" t="n">
         <v>0.00249790765199937</v>
@@ -2386,13 +2386,13 @@
         <v>0.0009706099471540908</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.002140702279316488</v>
+        <v>0.002140702279316489</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0005368475107017046</v>
+        <v>0.0005368475107017044</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0008884642663115442</v>
+        <v>0.0008884642663115443</v>
       </c>
       <c r="DX4" t="n">
         <v>0.000840275081841446</v>
@@ -2401,19 +2401,19 @@
         <v>0.0002479840870246737</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0003504888700205975</v>
+        <v>0.0003504888700205976</v>
       </c>
       <c r="EA4" t="n">
         <v>0.0006578585030704757</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.000422047596441051</v>
+        <v>0.0004220475964410509</v>
       </c>
       <c r="EC4" t="n">
         <v>0.008324093999602898</v>
       </c>
       <c r="ED4" t="n">
-        <v>5.071108653510646e-05</v>
+        <v>5.071108653510645e-05</v>
       </c>
       <c r="EE4" t="n">
         <v>0.0001291663713192107</v>
@@ -2425,10 +2425,10 @@
         <v>0.0002386510802927683</v>
       </c>
       <c r="EH4" t="n">
-        <v>8.996123483941838e-05</v>
+        <v>8.996123483941835e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>6.563718081817266e-05</v>
+        <v>6.563718081817265e-05</v>
       </c>
       <c r="EJ4" t="n">
         <v>3.632718925178742e-05</v>
@@ -2467,13 +2467,13 @@
         <v>0.1832848072933106</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4974677757564174</v>
+        <v>0.4974677757564172</v>
       </c>
       <c r="H5" t="n">
         <v>0.1922909266699243</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01604696364747974</v>
+        <v>0.01604696364747973</v>
       </c>
       <c r="J5" t="n">
         <v>0.03500951930393774</v>
@@ -2482,7 +2482,7 @@
         <v>0.01238761467382233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05438336181778324</v>
+        <v>0.05438336181778328</v>
       </c>
       <c r="M5" t="n">
         <v>0.01362312684900071</v>
@@ -2497,7 +2497,7 @@
         <v>0.01295269466518753</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003224765454510761</v>
+        <v>0.003224765454510762</v>
       </c>
       <c r="R5" t="n">
         <v>0.007582446349790083</v>
@@ -2515,10 +2515,10 @@
         <v>0.001928058058319809</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01498242419514372</v>
+        <v>0.01498242419514373</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002332557460290045</v>
+        <v>0.0002332557460290044</v>
       </c>
       <c r="Y5" t="n">
         <v>0.003476660197740436</v>
@@ -2527,13 +2527,13 @@
         <v>0.0051441315682254</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01903177565802752</v>
+        <v>0.0190317756580275</v>
       </c>
       <c r="AB5" t="n">
         <v>0.001405524036024706</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.06106752647625596</v>
+        <v>0.06106752647625598</v>
       </c>
       <c r="AD5" t="n">
         <v>6.5986834375038e-05</v>
@@ -2542,10 +2542,10 @@
         <v>3.420052838903571e-05</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.05038234324876485</v>
+        <v>0.05038234324876489</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.02958781294552846</v>
+        <v>0.02958781294552845</v>
       </c>
       <c r="AH5" t="n">
         <v>0.003050272939585802</v>
@@ -2554,10 +2554,10 @@
         <v>0.001132765628089293</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.003046817855219002</v>
+        <v>0.003046817855219001</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.01754619713144224</v>
+        <v>0.01754619713144223</v>
       </c>
       <c r="AL5" t="n">
         <v>0.001839833503065442</v>
@@ -2575,7 +2575,7 @@
         <v>0.001257439907088811</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.003745369472464469</v>
+        <v>0.003745369472464467</v>
       </c>
       <c r="AR5" t="n">
         <v>0.006613049785733164</v>
@@ -2584,7 +2584,7 @@
         <v>6.339709492786703e-05</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0003614314130918455</v>
+        <v>0.0003614314130918456</v>
       </c>
       <c r="AU5" t="n">
         <v>0.0003991968408366196</v>
@@ -2602,19 +2602,19 @@
         <v>0.03761740724333319</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0008191105150907963</v>
+        <v>0.0008191105150907964</v>
       </c>
       <c r="BA5" t="n">
         <v>0.0003107353153499921</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.04407038471159335</v>
+        <v>0.04407038471159334</v>
       </c>
       <c r="BC5" t="n">
         <v>0.01506560063388713</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01262006387445932</v>
+        <v>0.01262006387445931</v>
       </c>
       <c r="BE5" t="n">
         <v>0.001745828216746097</v>
@@ -2623,13 +2623,13 @@
         <v>0.001718985082566435</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.001867253562487279</v>
+        <v>0.00186725356248728</v>
       </c>
       <c r="BH5" t="n">
         <v>0.01072635275071449</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0007284460527268111</v>
+        <v>0.0007284460527268109</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.0005971221126968319</v>
@@ -2650,10 +2650,10 @@
         <v>0.0001169248531402528</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0005873239981161159</v>
+        <v>0.0005873239981161157</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0008058698666449622</v>
+        <v>0.0008058698666449625</v>
       </c>
       <c r="BR5" t="n">
         <v>0.0009290777632388774</v>
@@ -2665,7 +2665,7 @@
         <v>0.005406644575785067</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.005664354278832955</v>
+        <v>0.005664354278832953</v>
       </c>
       <c r="BV5" t="n">
         <v>0.004839135275689604</v>
@@ -2683,7 +2683,7 @@
         <v>0.02915803593581146</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0002640283468310355</v>
+        <v>0.0002640283468310357</v>
       </c>
       <c r="CB5" t="n">
         <v>0.0004957776840081843</v>
@@ -2710,7 +2710,7 @@
         <v>0.0003352146068014832</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.01769684819762537</v>
+        <v>0.01769684819762538</v>
       </c>
       <c r="CK5" t="n">
         <v>5.1795417673977e-05</v>
@@ -2719,10 +2719,10 @@
         <v>0.00163765119331058</v>
       </c>
       <c r="CM5" t="n">
-        <v>5.740158734129223e-05</v>
+        <v>5.740158734129224e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0004202960483021874</v>
+        <v>0.0004202960483021873</v>
       </c>
       <c r="CO5" t="n">
         <v>0.0006214515755795044</v>
@@ -2740,7 +2740,7 @@
         <v>0.000131028255136034</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0005050644452634369</v>
+        <v>0.000505064445263437</v>
       </c>
       <c r="CU5" t="n">
         <v>0.0002534839185108084</v>
@@ -2752,7 +2752,7 @@
         <v>0.0004599818491270817</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.00438491452241845</v>
+        <v>0.004384914522418451</v>
       </c>
       <c r="CY5" t="n">
         <v>0.0002150730033617087</v>
@@ -2764,19 +2764,19 @@
         <v>0.001005062345810777</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0008379034428604674</v>
+        <v>0.0008379034428604675</v>
       </c>
       <c r="DC5" t="n">
         <v>5.857288491736612e-05</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.002751110538380998</v>
+        <v>0.002751110538380999</v>
       </c>
       <c r="DE5" t="n">
         <v>0.0001704999385044117</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.001882145053822496</v>
+        <v>0.001882145053822497</v>
       </c>
       <c r="DG5" t="n">
         <v>0.01105268264390292</v>
@@ -2797,7 +2797,7 @@
         <v>0.0003996388737403179</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0007959779737154494</v>
+        <v>0.0007959779737154495</v>
       </c>
       <c r="DN5" t="n">
         <v>5.169619128614461e-05</v>
@@ -2806,7 +2806,7 @@
         <v>0.002316521724466292</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.08445236644989623</v>
+        <v>0.08445236644989626</v>
       </c>
       <c r="DQ5" t="n">
         <v>3.332754700192381e-05</v>
@@ -2857,13 +2857,13 @@
         <v>2.301894193843465e-05</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0003162716753798483</v>
+        <v>0.0003162716753798484</v>
       </c>
       <c r="EH5" t="n">
         <v>0.0001433828800304166</v>
       </c>
       <c r="EI5" t="n">
-        <v>7.545449284953233e-05</v>
+        <v>7.545449284953232e-05</v>
       </c>
       <c r="EJ5" t="n">
         <v>5.402660075889315e-05</v>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3559765301098404</v>
+        <v>0.3559765301098403</v>
       </c>
       <c r="C6" t="n">
         <v>0.001378754660338261</v>
@@ -2899,10 +2899,10 @@
         <v>0.03567966981741302</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1744910764837265</v>
+        <v>0.1744910764837267</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4940064743004003</v>
+        <v>0.4940064743003997</v>
       </c>
       <c r="H6" t="n">
         <v>0.1679976866198876</v>
@@ -2917,13 +2917,13 @@
         <v>0.0099903095590981</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05141612972900081</v>
+        <v>0.05141612972900082</v>
       </c>
       <c r="M6" t="n">
         <v>0.01274488917665001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01829061189428671</v>
+        <v>0.0182906118942867</v>
       </c>
       <c r="O6" t="n">
         <v>0.002230850150217093</v>
@@ -2938,7 +2938,7 @@
         <v>0.007525443789274805</v>
       </c>
       <c r="S6" t="n">
-        <v>0.006695000836577082</v>
+        <v>0.006695000836577081</v>
       </c>
       <c r="T6" t="n">
         <v>0.02220033555120176</v>
@@ -2956,19 +2956,19 @@
         <v>0.0002343108480085284</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003216228101358317</v>
+        <v>0.003216228101358316</v>
       </c>
       <c r="Z6" t="n">
         <v>0.005496532609139635</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01816839068838072</v>
+        <v>0.01816839068838073</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001324056773634768</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06363532686346259</v>
+        <v>0.06363532686346263</v>
       </c>
       <c r="AD6" t="n">
         <v>6.798486235701442e-05</v>
@@ -2977,13 +2977,13 @@
         <v>3.295747315510672e-05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.04993537163229205</v>
+        <v>0.04993537163229206</v>
       </c>
       <c r="AG6" t="n">
         <v>0.02310378264756585</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.002701862619500335</v>
+        <v>0.002701862619500334</v>
       </c>
       <c r="AI6" t="n">
         <v>0.0008813255883615365</v>
@@ -2992,13 +2992,13 @@
         <v>0.002978688723026406</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.02018352660108584</v>
+        <v>0.02018352660108585</v>
       </c>
       <c r="AL6" t="n">
         <v>0.001838557028409628</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0003613415606113759</v>
+        <v>0.0003613415606113761</v>
       </c>
       <c r="AN6" t="n">
         <v>0.0002604996700505414</v>
@@ -3007,7 +3007,7 @@
         <v>0.001383733937405727</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.001026413051192482</v>
+        <v>0.001026413051192483</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.002779624886213802</v>
@@ -3019,7 +3019,7 @@
         <v>5.937622569107978e-05</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0003140327276658464</v>
+        <v>0.0003140327276658465</v>
       </c>
       <c r="AU6" t="n">
         <v>0.000375658155957796</v>
@@ -3034,13 +3034,13 @@
         <v>0.001384046987299332</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.04489240818612219</v>
+        <v>0.0448924081861222</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.0007018822935937685</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0003186355394198096</v>
+        <v>0.0003186355394198098</v>
       </c>
       <c r="BB6" t="n">
         <v>0.03367427063012116</v>
@@ -3082,13 +3082,13 @@
         <v>0.002097987241980925</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0001082506515395764</v>
+        <v>0.0001082506515395765</v>
       </c>
       <c r="BP6" t="n">
         <v>0.0005140636186815319</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0006196285052672798</v>
+        <v>0.0006196285052672797</v>
       </c>
       <c r="BR6" t="n">
         <v>0.001064059459121359</v>
@@ -3100,13 +3100,13 @@
         <v>0.00544692458977884</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.005482678624033165</v>
+        <v>0.005482678624033167</v>
       </c>
       <c r="BV6" t="n">
         <v>0.00392118439658188</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.355821576237171e-05</v>
+        <v>3.35582157623717e-05</v>
       </c>
       <c r="BX6" t="n">
         <v>0.001792998780406594</v>
@@ -3166,7 +3166,7 @@
         <v>0.001001575197170887</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.00156876760876013</v>
+        <v>0.001568767608760131</v>
       </c>
       <c r="CR6" t="n">
         <v>0.0004615693796872052</v>
@@ -3229,10 +3229,10 @@
         <v>0.002096024928365661</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0003452849446034507</v>
+        <v>0.0003452849446034506</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0004062882882338531</v>
+        <v>0.000406288288233853</v>
       </c>
       <c r="DN6" t="n">
         <v>5.043319776536446e-05</v>
@@ -3256,7 +3256,7 @@
         <v>0.001815086518229008</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.003527097110290303</v>
+        <v>0.003527097110290302</v>
       </c>
       <c r="DV6" t="n">
         <v>0.0007885700812343681</v>
@@ -3268,16 +3268,16 @@
         <v>0.001106492855203367</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0002317177684017595</v>
+        <v>0.0002317177684017594</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0004649150703924183</v>
+        <v>0.0004649150703924182</v>
       </c>
       <c r="EA6" t="n">
         <v>0.0005706064108255011</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0005018882575982626</v>
+        <v>0.0005018882575982627</v>
       </c>
       <c r="EC6" t="n">
         <v>0.0150829067750236</v>
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3616973321520129</v>
+        <v>0.3616973321520134</v>
       </c>
       <c r="C7" t="n">
         <v>0.001373063284887813</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001848820701685508</v>
+        <v>0.001848820701685509</v>
       </c>
       <c r="E7" t="n">
         <v>0.03844697540226989</v>
@@ -3337,7 +3337,7 @@
         <v>0.1697021620370526</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4892953541991773</v>
+        <v>0.4892953541991772</v>
       </c>
       <c r="H7" t="n">
         <v>0.1791137540263069</v>
@@ -3349,13 +3349,13 @@
         <v>0.03359434022454191</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01080203807826756</v>
+        <v>0.01080203807826755</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05173207640148293</v>
+        <v>0.05173207640148295</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01242772029022884</v>
+        <v>0.01242772029022885</v>
       </c>
       <c r="N7" t="n">
         <v>0.0188585863509152</v>
@@ -3364,19 +3364,19 @@
         <v>0.0025340578833191</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01179702216080809</v>
+        <v>0.0117970221608081</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003151882828460583</v>
+        <v>0.003151882828460585</v>
       </c>
       <c r="R7" t="n">
         <v>0.00747835788304578</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006877918622446228</v>
+        <v>0.006877918622446233</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02338085889977004</v>
+        <v>0.02338085889977005</v>
       </c>
       <c r="U7" t="n">
         <v>0.0001538682995691823</v>
@@ -3385,34 +3385,34 @@
         <v>0.001851825937622066</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01371103519092737</v>
+        <v>0.01371103519092738</v>
       </c>
       <c r="X7" t="n">
         <v>0.0002367649068369786</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003366688965504633</v>
+        <v>0.003366688965504634</v>
       </c>
       <c r="Z7" t="n">
         <v>0.005336986931036639</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0196590304286626</v>
+        <v>0.01965903042866259</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001390744191897979</v>
+        <v>0.00139074419189798</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05751627789386161</v>
+        <v>0.05751627789386164</v>
       </c>
       <c r="AD7" t="n">
         <v>6.68060488343329e-05</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.439757481255416e-05</v>
+        <v>3.439757481255417e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.05220280695474431</v>
+        <v>0.05220280695474434</v>
       </c>
       <c r="AG7" t="n">
         <v>0.02486465547451934</v>
@@ -3424,7 +3424,7 @@
         <v>0.0009428694351277463</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.003084699840287305</v>
+        <v>0.003084699840287304</v>
       </c>
       <c r="AK7" t="n">
         <v>0.02083896394982996</v>
@@ -3445,7 +3445,7 @@
         <v>0.00105091078212547</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.003203256996161851</v>
+        <v>0.003203256996161852</v>
       </c>
       <c r="AR7" t="n">
         <v>0.006530170469221316</v>
@@ -3469,7 +3469,7 @@
         <v>0.001372799585074024</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.04485733347319811</v>
+        <v>0.0448573334731981</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.0007342706849197473</v>
@@ -3478,13 +3478,13 @@
         <v>0.0003028818895426459</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.03538229842722888</v>
+        <v>0.03538229842722889</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.01203076578369929</v>
+        <v>0.0120307657836993</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01806060978014847</v>
+        <v>0.01806060978014848</v>
       </c>
       <c r="BE7" t="n">
         <v>0.001479733313999956</v>
@@ -3496,10 +3496,10 @@
         <v>0.001911367862094573</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.009933543160497398</v>
+        <v>0.009933543160497391</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0006074986122925704</v>
+        <v>0.0006074986122925703</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.0007362143741839885</v>
@@ -3508,16 +3508,16 @@
         <v>0.009094774958445934</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0001859488650466923</v>
+        <v>0.0001859488650466922</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0306093119953407</v>
+        <v>0.03060931199534069</v>
       </c>
       <c r="BN7" t="n">
         <v>0.002149051774726496</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0001028524430702221</v>
+        <v>0.000102852443070222</v>
       </c>
       <c r="BP7" t="n">
         <v>0.0005300158437942501</v>
@@ -3529,7 +3529,7 @@
         <v>0.0008685513261982774</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.01131553973951997</v>
+        <v>0.01131553973951998</v>
       </c>
       <c r="BT7" t="n">
         <v>0.006030814723802178</v>
@@ -3541,7 +3541,7 @@
         <v>0.004192245394739303</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.855590830866796e-05</v>
+        <v>3.855590830866798e-05</v>
       </c>
       <c r="BX7" t="n">
         <v>0.001839795264559137</v>
@@ -3556,13 +3556,13 @@
         <v>0.0002618453242897324</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0004179813924042926</v>
+        <v>0.0004179813924042927</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0001741180367564559</v>
+        <v>0.0001741180367564558</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0004183774307009282</v>
+        <v>0.0004183774307009281</v>
       </c>
       <c r="CE7" t="n">
         <v>0.008195495978784103</v>
@@ -3571,7 +3571,7 @@
         <v>0.001070142199452228</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.009290908223826786</v>
+        <v>0.009290908223826779</v>
       </c>
       <c r="CH7" t="n">
         <v>0.0009083841108493771</v>
@@ -3592,7 +3592,7 @@
         <v>7.305619899897802e-05</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0004151270559305388</v>
+        <v>0.000415127055930539</v>
       </c>
       <c r="CO7" t="n">
         <v>0.0005524258058129803</v>
@@ -3613,7 +3613,7 @@
         <v>0.000584909347589169</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0003813312200784449</v>
+        <v>0.000381331220078445</v>
       </c>
       <c r="CV7" t="n">
         <v>0.0006149904663173819</v>
@@ -3658,7 +3658,7 @@
         <v>0.000118402532937222</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0002917978935498035</v>
+        <v>0.0002917978935498036</v>
       </c>
       <c r="DK7" t="n">
         <v>0.002323168031998054</v>
@@ -3673,7 +3673,7 @@
         <v>4.921790980357102e-05</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.003004758354095033</v>
+        <v>0.003004758354095035</v>
       </c>
       <c r="DP7" t="n">
         <v>0.09697002307929983</v>
@@ -3691,7 +3691,7 @@
         <v>0.001630944706078845</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.003407781384557602</v>
+        <v>0.003407781384557601</v>
       </c>
       <c r="DV7" t="n">
         <v>0.000784503653645748</v>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.361478016164669</v>
+        <v>0.3614780161646688</v>
       </c>
       <c r="C8" t="n">
         <v>0.001392408343939392</v>
@@ -3772,10 +3772,10 @@
         <v>0.1705288408211066</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5010929176068742</v>
+        <v>0.5010929176068744</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1819542757754737</v>
+        <v>0.1819542757754735</v>
       </c>
       <c r="I8" t="n">
         <v>0.01305656517458865</v>
@@ -3784,7 +3784,7 @@
         <v>0.03292390324278308</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01053657061366469</v>
+        <v>0.01053657061366468</v>
       </c>
       <c r="L8" t="n">
         <v>0.05233916209310856</v>
@@ -3793,7 +3793,7 @@
         <v>0.01297969573764256</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01964430850891793</v>
+        <v>0.01964430850891795</v>
       </c>
       <c r="O8" t="n">
         <v>0.002743563738312651</v>
@@ -3805,19 +3805,19 @@
         <v>0.003123697486757893</v>
       </c>
       <c r="R8" t="n">
-        <v>0.007240553950184899</v>
+        <v>0.007240553950184896</v>
       </c>
       <c r="S8" t="n">
         <v>0.006769068302873928</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02124143526100867</v>
+        <v>0.02124143526100869</v>
       </c>
       <c r="U8" t="n">
         <v>0.0001578248243646006</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001898806197146921</v>
+        <v>0.001898806197146922</v>
       </c>
       <c r="W8" t="n">
         <v>0.01493396759651654</v>
@@ -3826,10 +3826,10 @@
         <v>0.0002236040023456802</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003185528854659408</v>
+        <v>0.003185528854659407</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.005199178536030591</v>
+        <v>0.005199178536030589</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01977961876595257</v>
@@ -3838,10 +3838,10 @@
         <v>0.001389534465788636</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.06018014540871497</v>
+        <v>0.06018014540871494</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.577213690896524e-05</v>
+        <v>6.577213690896522e-05</v>
       </c>
       <c r="AE8" t="n">
         <v>3.472726258442438e-05</v>
@@ -3865,7 +3865,7 @@
         <v>0.01846562154358657</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001757761976454658</v>
+        <v>0.001757761976454659</v>
       </c>
       <c r="AM8" t="n">
         <v>0.0003430599983697722</v>
@@ -3874,7 +3874,7 @@
         <v>0.0002732865025095966</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001429652514494395</v>
+        <v>0.001429652514494397</v>
       </c>
       <c r="AP8" t="n">
         <v>0.0010828060949582</v>
@@ -3883,13 +3883,13 @@
         <v>0.00305210010938391</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.006515197046603008</v>
+        <v>0.006515197046603005</v>
       </c>
       <c r="AS8" t="n">
         <v>6.218673563640139e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0003130146929285173</v>
+        <v>0.0003130146929285172</v>
       </c>
       <c r="AU8" t="n">
         <v>0.0003912377863052071</v>
@@ -3907,13 +3907,13 @@
         <v>0.04219469786854742</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0008515410927912178</v>
+        <v>0.000851541092791218</v>
       </c>
       <c r="BA8" t="n">
         <v>0.0003003059322044278</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.03763131538072371</v>
+        <v>0.03763131538072374</v>
       </c>
       <c r="BC8" t="n">
         <v>0.0123026838404237</v>
@@ -3922,7 +3922,7 @@
         <v>0.0143000897894021</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001619933018950415</v>
+        <v>0.001619933018950416</v>
       </c>
       <c r="BF8" t="n">
         <v>0.001414754152060769</v>
@@ -3934,19 +3934,19 @@
         <v>0.01072106038231166</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0006638297347294061</v>
+        <v>0.000663829734729406</v>
       </c>
       <c r="BJ8" t="n">
         <v>0.0006426347094806681</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.009763937830748456</v>
+        <v>0.009763937830748448</v>
       </c>
       <c r="BL8" t="n">
         <v>0.0001811579619540046</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.02821774915555954</v>
+        <v>0.02821774915555953</v>
       </c>
       <c r="BN8" t="n">
         <v>0.002066258087936079</v>
@@ -3967,7 +3967,7 @@
         <v>0.01238580143779191</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.005233142608453798</v>
+        <v>0.005233142608453797</v>
       </c>
       <c r="BU8" t="n">
         <v>0.005647507973007072</v>
@@ -3976,7 +3976,7 @@
         <v>0.004249638049626335</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.21396621371968e-05</v>
+        <v>3.213966213719681e-05</v>
       </c>
       <c r="BX8" t="n">
         <v>0.001841563092622233</v>
@@ -3988,16 +3988,16 @@
         <v>0.02996290848989883</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0002572270552155942</v>
+        <v>0.0002572270552155944</v>
       </c>
       <c r="CB8" t="n">
         <v>0.0004538736245372539</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0001822771061250901</v>
+        <v>0.00018227710612509</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0003497489513968448</v>
+        <v>0.0003497489513968446</v>
       </c>
       <c r="CE8" t="n">
         <v>0.008967740343371999</v>
@@ -4006,7 +4006,7 @@
         <v>0.001144905449238564</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.00991284707038694</v>
+        <v>0.009912847070386942</v>
       </c>
       <c r="CH8" t="n">
         <v>0.0009938693279002105</v>
@@ -4024,7 +4024,7 @@
         <v>0.001504917865565166</v>
       </c>
       <c r="CM8" t="n">
-        <v>5.576607935225832e-05</v>
+        <v>5.576607935225831e-05</v>
       </c>
       <c r="CN8" t="n">
         <v>0.0004046873963303452</v>
@@ -4033,7 +4033,7 @@
         <v>0.0006471562753665132</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0007802389624300078</v>
+        <v>0.0007802389624300079</v>
       </c>
       <c r="CQ8" t="n">
         <v>0.001230721899870617</v>
@@ -4072,10 +4072,10 @@
         <v>0.0007910649998152807</v>
       </c>
       <c r="DC8" t="n">
-        <v>6.303864519331283e-05</v>
+        <v>6.303864519331281e-05</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.002794799753451129</v>
+        <v>0.002794799753451128</v>
       </c>
       <c r="DE8" t="n">
         <v>0.000167861310837444</v>
@@ -4111,16 +4111,16 @@
         <v>0.0025586432033828</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.09419826439270973</v>
+        <v>0.09419826439270976</v>
       </c>
       <c r="DQ8" t="n">
         <v>3.148659225065586e-05</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001217149295216939</v>
+        <v>0.000121714929521694</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.001966066983778737</v>
+        <v>0.001966066983778735</v>
       </c>
       <c r="DT8" t="n">
         <v>0.001536057013027726</v>
@@ -4129,7 +4129,7 @@
         <v>0.003315442142201076</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0007319040686379</v>
+        <v>0.0007319040686378999</v>
       </c>
       <c r="DW8" t="n">
         <v>0.001242510734792359</v>
@@ -4159,7 +4159,7 @@
         <v>0.0001655398674323992</v>
       </c>
       <c r="EF8" t="n">
-        <v>2.256814619700117e-05</v>
+        <v>2.256814619700119e-05</v>
       </c>
       <c r="EG8" t="n">
         <v>0.0003029356147264279</v>
@@ -4168,7 +4168,7 @@
         <v>0.0001433528988107874</v>
       </c>
       <c r="EI8" t="n">
-        <v>7.631418927691154e-05</v>
+        <v>7.631418927691156e-05</v>
       </c>
       <c r="EJ8" t="n">
         <v>5.186079722929393e-05</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3697712239747263</v>
+        <v>0.3697712239747261</v>
       </c>
       <c r="C9" t="n">
         <v>0.001461218296793041</v>
@@ -4204,13 +4204,13 @@
         <v>0.04001168192944252</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1843521940566766</v>
+        <v>0.1843521940566765</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4920509336778487</v>
+        <v>0.4920509336778492</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1950488683076636</v>
+        <v>0.1950488683076637</v>
       </c>
       <c r="I9" t="n">
         <v>0.01670031640864167</v>
@@ -4219,10 +4219,10 @@
         <v>0.0325162614254812</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01328018374486239</v>
+        <v>0.0132801837448624</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05318966227280726</v>
+        <v>0.05318966227280729</v>
       </c>
       <c r="M9" t="n">
         <v>0.01277366436307569</v>
@@ -4231,7 +4231,7 @@
         <v>0.02065614185206344</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002802238496253389</v>
+        <v>0.00280223849625339</v>
       </c>
       <c r="P9" t="n">
         <v>0.01184068921238392</v>
@@ -4243,10 +4243,10 @@
         <v>0.007613628872687188</v>
       </c>
       <c r="S9" t="n">
-        <v>0.007257440205810479</v>
+        <v>0.007257440205810481</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02271422063637896</v>
+        <v>0.02271422063637894</v>
       </c>
       <c r="U9" t="n">
         <v>0.0001520451887078564</v>
@@ -4261,10 +4261,10 @@
         <v>0.0002230735727357064</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003511619059138761</v>
+        <v>0.003511619059138762</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.005149533606936168</v>
+        <v>0.005149533606936167</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01766204664759897</v>
@@ -4273,7 +4273,7 @@
         <v>0.001358423529721423</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0601476023232725</v>
+        <v>0.06014760232327248</v>
       </c>
       <c r="AD9" t="n">
         <v>6.346753345277737e-05</v>
@@ -4282,7 +4282,7 @@
         <v>3.145447001136385e-05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0488864246372236</v>
+        <v>0.04888642463722358</v>
       </c>
       <c r="AG9" t="n">
         <v>0.03365168707637019</v>
@@ -4291,13 +4291,13 @@
         <v>0.003034295259340324</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.001124817482863579</v>
+        <v>0.00112481748286358</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.002930978928564624</v>
+        <v>0.002930978928564623</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01972568503579264</v>
+        <v>0.01972568503579263</v>
       </c>
       <c r="AL9" t="n">
         <v>0.001748338111495326</v>
@@ -4309,7 +4309,7 @@
         <v>0.0003190562087911122</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001598223016039847</v>
+        <v>0.001598223016039848</v>
       </c>
       <c r="AP9" t="n">
         <v>0.001191754414735129</v>
@@ -4318,7 +4318,7 @@
         <v>0.00381278888731524</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.006423593791213469</v>
+        <v>0.006423593791213468</v>
       </c>
       <c r="AS9" t="n">
         <v>6.268828405107488e-05</v>
@@ -4333,7 +4333,7 @@
         <v>0.002992196434234022</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0191317771403957</v>
+        <v>0.01913177714039571</v>
       </c>
       <c r="AX9" t="n">
         <v>0.001228198512256292</v>
@@ -4348,7 +4348,7 @@
         <v>0.000290529185672727</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.04149039456243861</v>
+        <v>0.0414903945624386</v>
       </c>
       <c r="BC9" t="n">
         <v>0.0137420391066276</v>
@@ -4369,7 +4369,7 @@
         <v>0.01047524794068949</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0007223736761531612</v>
+        <v>0.0007223736761531611</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.0006070397836695424</v>
@@ -4381,16 +4381,16 @@
         <v>0.0002283141938052</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.02807735250508187</v>
+        <v>0.02807735250508188</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.002314544509348281</v>
+        <v>0.002314544509348279</v>
       </c>
       <c r="BO9" t="n">
         <v>0.0001102294505001531</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0005503246569777786</v>
+        <v>0.0005503246569777788</v>
       </c>
       <c r="BQ9" t="n">
         <v>0.0007628947975890241</v>
@@ -4402,13 +4402,13 @@
         <v>0.01335947588725805</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.005462692860165888</v>
+        <v>0.005462692860165885</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.00605342333201403</v>
+        <v>0.006053423332014028</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.00480393277735597</v>
+        <v>0.004803932777355969</v>
       </c>
       <c r="BW9" t="n">
         <v>4.447498595534028e-05</v>
@@ -4441,13 +4441,13 @@
         <v>0.001223363094285114</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.009908652944542126</v>
+        <v>0.009908652944542122</v>
       </c>
       <c r="CH9" t="n">
         <v>0.0009286692539576117</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.000360802265466141</v>
+        <v>0.0003608022654661409</v>
       </c>
       <c r="CJ9" t="n">
         <v>0.01671078138550671</v>
@@ -4462,16 +4462,16 @@
         <v>5.876074023640461e-05</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0003952359291027665</v>
+        <v>0.0003952359291027666</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0005532044898811257</v>
+        <v>0.0005532044898811259</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0008288201338415135</v>
+        <v>0.0008288201338415134</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001400752757600807</v>
+        <v>0.001400752757600808</v>
       </c>
       <c r="CR9" t="n">
         <v>0.0005052977084871318</v>
@@ -4498,7 +4498,7 @@
         <v>0.0002091924317925715</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0005071225865893231</v>
+        <v>0.0005071225865893232</v>
       </c>
       <c r="DA9" t="n">
         <v>0.001072238823430902</v>
@@ -4546,7 +4546,7 @@
         <v>0.002485268533908817</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.08211157920822963</v>
+        <v>0.08211157920822967</v>
       </c>
       <c r="DQ9" t="n">
         <v>3.164482429812269e-05</v>
@@ -4564,7 +4564,7 @@
         <v>0.003288521961253711</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.000705215709396933</v>
+        <v>0.0007052157093969332</v>
       </c>
       <c r="DW9" t="n">
         <v>0.001127858259784538</v>
@@ -4576,7 +4576,7 @@
         <v>0.0002317235700291241</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0004473471999959775</v>
+        <v>0.0004473471999959774</v>
       </c>
       <c r="EA9" t="n">
         <v>0.00050592800725357</v>
@@ -4588,7 +4588,7 @@
         <v>0.01295262108283822</v>
       </c>
       <c r="ED9" t="n">
-        <v>3.568468592521138e-05</v>
+        <v>3.568468592521136e-05</v>
       </c>
       <c r="EE9" t="n">
         <v>0.0001534095487238344</v>
@@ -4603,7 +4603,7 @@
         <v>0.0001404511773355288</v>
       </c>
       <c r="EI9" t="n">
-        <v>6.990889904498655e-05</v>
+        <v>6.990889904498652e-05</v>
       </c>
       <c r="EJ9" t="n">
         <v>5.148948414833697e-05</v>
